--- a/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00126_19130805/oocihm.N_00126_19130805.8.xlsx
+++ b/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00126_19130805/oocihm.N_00126_19130805.8.xlsx
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00126_19130805/oocihm.N_00126_19130805.8.xlsx
+++ b/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00126_19130805/oocihm.N_00126_19130805.8.xlsx
@@ -416,14 +416,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y35"/>
+  <dimension ref="A1:Y39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
     <col width="60" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
     <col width="60" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
@@ -431,11 +431,11 @@
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="60" customWidth="1" min="14" max="14"/>
     <col width="60" customWidth="1" min="15" max="15"/>
     <col width="60" customWidth="1" min="16" max="16"/>
-    <col width="53" customWidth="1" min="17" max="17"/>
+    <col width="60" customWidth="1" min="17" max="17"/>
     <col width="30" customWidth="1" min="18" max="18"/>
     <col width="60" customWidth="1" min="19" max="19"/>
     <col width="30" customWidth="1" min="20" max="20"/>
@@ -597,7 +597,7 @@
       <c r="E2" s="1" t="inlineStr"/>
       <c r="F2" s="1" t="inlineStr">
         <is>
-          <t>L607: candidate OCR token mismatch vs other OCR: "Kimg" vs "King" :: at the Gaiety last evening, " Kimg of</t>
+          <t>L521: candidate OCR token mismatch vs other OCR: "evening'sr" vs "evening’s" :: At last evening'sr</t>
         </is>
       </c>
       <c r="G2" s="1" t="inlineStr">
@@ -617,24 +617,28 @@
       </c>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>L10: stray/suspicious non-ASCII glyph(s): U+00A2 CENT SIGN | isolated marker/symbol line :: â‘¢</t>
+          <t>L2: stray/suspicious non-ASCII glyph(s): U+2212 MINUS SIGN | isolated marker/symbol line :: −</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L3: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
-          <t>L3: isolated marker/symbol line :: 2</t>
+          <t>L2: stray/suspicious non-ASCII glyph(s): U+2212 MINUS SIGN | isolated marker/symbol line :: −</t>
         </is>
       </c>
       <c r="O2" s="1" t="inlineStr">
         <is>
-          <t>L1: isolated marker/symbol line :: ï»¿</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]</t>
         </is>
       </c>
       <c r="P2" s="1" t="inlineStr">
@@ -650,7 +654,7 @@
       <c r="R2" s="1" t="inlineStr"/>
       <c r="S2" s="1" t="inlineStr">
         <is>
-          <t>L51: line starts with punctuation glued to text :: *nesday.0</t>
+          <t>L48: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • Moderate to fresh northerly to •</t>
         </is>
       </c>
       <c r="T2" s="1" t="inlineStr"/>
@@ -677,14 +681,14 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>828</t>
+          <t>603</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
       <c r="E3" s="1" t="inlineStr"/>
       <c r="F3" s="1" t="inlineStr">
         <is>
-          <t>L675: candidate OCR token mismatch vs other OCR: "Oity" vs "City" :: Opp. Oity Hall</t>
+          <t>L607: candidate OCR token mismatch vs other OCR: "Kimg" vs "King" :: at the Gaiety last evening, " Kimg of</t>
         </is>
       </c>
       <c r="G3" s="1" t="inlineStr">
@@ -704,24 +708,24 @@
       </c>
       <c r="J3" s="1" t="inlineStr">
         <is>
-          <t>L13: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA, U+00AD SOFT HYPHEN | isolated marker/symbol line :: ä¸­</t>
+          <t>L13: stray/suspicious non-ASCII glyph(s): U+4E2D CJK UNIFIED IDEOGRAPH-4E2D | isolated marker/symbol line :: 中</t>
         </is>
       </c>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>L47: stray/suspicious non-ASCII glyph(s): U+2122 TRADE MARK SIGN, U+00A6 BROKEN BAR, U+20AC EURO SIGN :: â™¦ Toronto, Aug. 5.â€”Maritime: Â°</t>
+          <t>L3: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr"/>
       <c r="M3" s="1" t="inlineStr"/>
       <c r="N3" s="1" t="inlineStr">
         <is>
-          <t>L9: isolated marker/symbol line :: 3</t>
+          <t>L3: isolated marker/symbol line :: 2</t>
         </is>
       </c>
       <c r="O3" s="1" t="inlineStr">
         <is>
-          <t>L3: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L3: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P3" s="1" t="inlineStr">
@@ -729,11 +733,15 @@
           <t>L515: punctuation artifact: repeated periods :: Lauchlan will perform the ceremony...</t>
         </is>
       </c>
-      <c r="Q3" s="1" t="inlineStr"/>
+      <c r="Q3" s="1" t="inlineStr">
+        <is>
+          <t>L50: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | punctuation artifact: hyphen/bullet debris | line starts with punctuation glued to text :: • ately warm today and cn Wed-•</t>
+        </is>
+      </c>
       <c r="R3" s="1" t="inlineStr"/>
       <c r="S3" s="1" t="inlineStr">
         <is>
-          <t>L66: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | line starts with punctuation glued to text :: _________â€¢</t>
+          <t>L49: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • westerly winds, fair and moder-°</t>
         </is>
       </c>
       <c r="T3" s="1" t="inlineStr"/>
@@ -761,7 +769,11 @@
       </c>
       <c r="D4" s="1" t="inlineStr"/>
       <c r="E4" s="1" t="inlineStr"/>
-      <c r="F4" s="1" t="inlineStr"/>
+      <c r="F4" s="1" t="inlineStr">
+        <is>
+          <t>L675: candidate OCR token mismatch vs other OCR: "Oity" vs "City" :: Opp. Oity Hall</t>
+        </is>
+      </c>
       <c r="G4" s="1" t="inlineStr">
         <is>
           <t>L803: localized OCR phrase divergence vs other OCR: "SHO" vs "III Vo FDELL" :: III Vo FDELL, Opp. City Hall</t>
@@ -779,19 +791,19 @@
       </c>
       <c r="J4" s="1" t="inlineStr">
         <is>
-          <t>L100: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
+          <t>L54: stray/suspicious non-ASCII glyph(s): U+5FC3 CJK UNIFIED IDEOGRAPH-5FC3 | isolated marker/symbol line :: 心</t>
         </is>
       </c>
       <c r="K4" s="1" t="inlineStr">
         <is>
-          <t>L48: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ Moderate to fresh northerly to â€¢</t>
+          <t>L47: stray/suspicious non-ASCII glyph(s): U+2666 BLACK DIAMOND SUIT :: ♦ Toronto, Aug. 5.—Maritime: °</t>
         </is>
       </c>
       <c r="L4" s="1" t="inlineStr"/>
       <c r="M4" s="1" t="inlineStr"/>
       <c r="N4" s="1" t="inlineStr">
         <is>
-          <t>L10: stray/suspicious non-ASCII glyph(s): U+00A2 CENT SIGN | isolated marker/symbol line :: â‘¢</t>
+          <t>L9: isolated marker/symbol line :: 3</t>
         </is>
       </c>
       <c r="O4" s="1" t="inlineStr">
@@ -804,7 +816,7 @@
       <c r="R4" s="1" t="inlineStr"/>
       <c r="S4" s="1" t="inlineStr">
         <is>
-          <t>L488: line starts with digit/letter garbage token | suspicious token(s): 1just (letter/digit mix) | candidate OCR token mismatch vs other OCR: "just" vs "1just" :: 1just as serviceable for business</t>
+          <t>L50: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | punctuation artifact: hyphen/bullet debris | line starts with punctuation glued to text :: • ately warm today and cn Wed-•</t>
         </is>
       </c>
       <c r="T4" s="1" t="inlineStr"/>
@@ -822,12 +834,12 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>61</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>55</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
@@ -846,19 +858,19 @@
       </c>
       <c r="J5" s="1" t="inlineStr">
         <is>
-          <t>L194: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: â€�</t>
+          <t>L100: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
         </is>
       </c>
       <c r="K5" s="1" t="inlineStr">
         <is>
-          <t>L49: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ westerly winds, fair and moder-Â°</t>
+          <t>L48: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • Moderate to fresh northerly to •</t>
         </is>
       </c>
       <c r="L5" s="1" t="inlineStr"/>
       <c r="M5" s="1" t="inlineStr"/>
       <c r="N5" s="1" t="inlineStr">
         <is>
-          <t>L12: isolated marker/symbol line :: 0</t>
+          <t>L10: isolated marker/symbol line :: ③</t>
         </is>
       </c>
       <c r="O5" s="1" t="inlineStr">
@@ -869,7 +881,11 @@
       <c r="P5" s="1" t="inlineStr"/>
       <c r="Q5" s="1" t="inlineStr"/>
       <c r="R5" s="1" t="inlineStr"/>
-      <c r="S5" s="1" t="inlineStr"/>
+      <c r="S5" s="1" t="inlineStr">
+        <is>
+          <t>L51: line starts with punctuation glued to text :: *nesday.0</t>
+        </is>
+      </c>
       <c r="T5" s="1" t="inlineStr"/>
       <c r="U5" s="1" t="inlineStr"/>
       <c r="V5" s="1" t="inlineStr"/>
@@ -909,19 +925,19 @@
       </c>
       <c r="J6" s="1" t="inlineStr">
         <is>
-          <t>L437: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | isolated marker/symbol line :: Â©</t>
+          <t>L193: stray/suspicious non-ASCII glyph(s): U+4EAB CJK UNIFIED IDEOGRAPH-4EAB | isolated marker/symbol line :: 享</t>
         </is>
       </c>
       <c r="K6" s="1" t="inlineStr">
         <is>
-          <t>L50: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ ately warm today and cn Wed-â€¢</t>
+          <t>L49: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • westerly winds, fair and moder-°</t>
         </is>
       </c>
       <c r="L6" s="1" t="inlineStr"/>
       <c r="M6" s="1" t="inlineStr"/>
       <c r="N6" s="1" t="inlineStr">
         <is>
-          <t>L13: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA, U+00AD SOFT HYPHEN | isolated marker/symbol line :: ä¸­</t>
+          <t>L12: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O6" s="1" t="inlineStr">
@@ -932,7 +948,11 @@
       <c r="P6" s="1" t="inlineStr"/>
       <c r="Q6" s="1" t="inlineStr"/>
       <c r="R6" s="1" t="inlineStr"/>
-      <c r="S6" s="1" t="inlineStr"/>
+      <c r="S6" s="1" t="inlineStr">
+        <is>
+          <t>L66: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | symbol-only separator/garbage line | line starts with punctuation glued to text :: _________•</t>
+        </is>
+      </c>
       <c r="T6" s="1" t="inlineStr"/>
       <c r="U6" s="1" t="inlineStr"/>
       <c r="V6" s="1" t="inlineStr"/>
@@ -972,19 +992,19 @@
       </c>
       <c r="J7" s="1" t="inlineStr">
         <is>
-          <t>L465: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: air is fresh and pureâ€”a tonic to</t>
+          <t>L437: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | isolated marker/symbol line :: ©</t>
         </is>
       </c>
       <c r="K7" s="1" t="inlineStr">
         <is>
-          <t>L66: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | line starts with punctuation glued to text :: _________â€¢</t>
+          <t>L50: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | punctuation artifact: hyphen/bullet debris | line starts with punctuation glued to text :: • ately warm today and cn Wed-•</t>
         </is>
       </c>
       <c r="L7" s="1" t="inlineStr"/>
       <c r="M7" s="1" t="inlineStr"/>
       <c r="N7" s="1" t="inlineStr">
         <is>
-          <t>L50: isolated marker/symbol line :: d</t>
+          <t>L13: stray/suspicious non-ASCII glyph(s): U+4E2D CJK UNIFIED IDEOGRAPH-4E2D | isolated marker/symbol line :: 中</t>
         </is>
       </c>
       <c r="O7" s="1" t="inlineStr">
@@ -995,7 +1015,11 @@
       <c r="P7" s="1" t="inlineStr"/>
       <c r="Q7" s="1" t="inlineStr"/>
       <c r="R7" s="1" t="inlineStr"/>
-      <c r="S7" s="1" t="inlineStr"/>
+      <c r="S7" s="1" t="inlineStr">
+        <is>
+          <t>L265: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • nell, K. F. Bonnell and Harry McFar-</t>
+        </is>
+      </c>
       <c r="T7" s="1" t="inlineStr"/>
       <c r="U7" s="1" t="inlineStr"/>
       <c r="V7" s="1" t="inlineStr"/>
@@ -1011,7 +1035,7 @@
       </c>
       <c r="B8" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C8" s="1" t="inlineStr">
@@ -1035,19 +1059,19 @@
       </c>
       <c r="J8" s="1" t="inlineStr">
         <is>
-          <t>L484: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: n $upward â€” depending</t>
+          <t>L492: stray/suspicious non-ASCII glyph(s): U+FF0C FULLWIDTH COMMA :: ， BRUSH</t>
         </is>
       </c>
       <c r="K8" s="1" t="inlineStr">
         <is>
-          <t>L175: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: VI. at St. Dunstanâ€™s school, who is</t>
+          <t>L66: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | symbol-only separator/garbage line | line starts with punctuation glued to text :: _________•</t>
         </is>
       </c>
       <c r="L8" s="1" t="inlineStr"/>
       <c r="M8" s="1" t="inlineStr"/>
       <c r="N8" s="1" t="inlineStr">
         <is>
-          <t>L76: isolated marker/symbol line :: 2</t>
+          <t>L50: isolated marker/symbol line :: d</t>
         </is>
       </c>
       <c r="O8" s="1" t="inlineStr">
@@ -1058,7 +1082,11 @@
       <c r="P8" s="1" t="inlineStr"/>
       <c r="Q8" s="1" t="inlineStr"/>
       <c r="R8" s="1" t="inlineStr"/>
-      <c r="S8" s="1" t="inlineStr"/>
+      <c r="S8" s="1" t="inlineStr">
+        <is>
+          <t>L488: line starts with digit/letter garbage token | suspicious token(s): 1just (letter/digit mix) | candidate OCR token mismatch vs other OCR: "just" vs "1just" :: 1just as serviceable for business</t>
+        </is>
+      </c>
       <c r="T8" s="1" t="inlineStr"/>
       <c r="U8" s="1" t="inlineStr"/>
       <c r="V8" s="1" t="inlineStr"/>
@@ -1098,19 +1126,19 @@
       </c>
       <c r="J9" s="1" t="inlineStr">
         <is>
-          <t>L631: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€” AT-</t>
+          <t>L677: stray/suspicious non-ASCII glyph(s): U+56FD CJK UNIFIED IDEOGRAPH-56FD | isolated marker/symbol line :: 国</t>
         </is>
       </c>
       <c r="K9" s="1" t="inlineStr">
         <is>
-          <t>L265: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ nell, K. F. Bonnell and Harry McFar-</t>
+          <t>L265: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • nell, K. F. Bonnell and Harry McFar-</t>
         </is>
       </c>
       <c r="L9" s="1" t="inlineStr"/>
       <c r="M9" s="1" t="inlineStr"/>
       <c r="N9" s="1" t="inlineStr">
         <is>
-          <t>L100: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
+          <t>L54: stray/suspicious non-ASCII glyph(s): U+5FC3 CJK UNIFIED IDEOGRAPH-5FC3 | isolated marker/symbol line :: 心</t>
         </is>
       </c>
       <c r="O9" s="1" t="inlineStr">
@@ -1137,12 +1165,12 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -1159,21 +1187,13 @@
           <t>L572: suspicious token(s): VanWart (odd internal casing) :: Mr. VanWart and his bride will re-</t>
         </is>
       </c>
-      <c r="J10" s="1" t="inlineStr">
-        <is>
-          <t>L666: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: oesâ€”Think Campbell's</t>
-        </is>
-      </c>
-      <c r="K10" s="1" t="inlineStr">
-        <is>
-          <t>L312: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€”.e usual contract.</t>
-        </is>
-      </c>
+      <c r="J10" s="1" t="inlineStr"/>
+      <c r="K10" s="1" t="inlineStr"/>
       <c r="L10" s="1" t="inlineStr"/>
       <c r="M10" s="1" t="inlineStr"/>
       <c r="N10" s="1" t="inlineStr">
         <is>
-          <t>L152: isolated marker/symbol line :: 8</t>
+          <t>L76: isolated marker/symbol line :: 2</t>
         </is>
       </c>
       <c r="O10" s="1" t="inlineStr">
@@ -1205,7 +1225,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1222,21 +1242,13 @@
           <t>L638: suspicious token(s): DeBaugh (odd internal casing) :: with Olga DeBaugh. Elsa von Bostel,</t>
         </is>
       </c>
-      <c r="J11" s="1" t="inlineStr">
-        <is>
-          <t>L689: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: ER OIL STOVES, equippÃ©d With</t>
-        </is>
-      </c>
-      <c r="K11" s="1" t="inlineStr">
-        <is>
-          <t>L318: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: A ladiesâ€™ swimming race has been :</t>
-        </is>
-      </c>
+      <c r="J11" s="1" t="inlineStr"/>
+      <c r="K11" s="1" t="inlineStr"/>
       <c r="L11" s="1" t="inlineStr"/>
       <c r="M11" s="1" t="inlineStr"/>
       <c r="N11" s="1" t="inlineStr">
         <is>
-          <t>L154: isolated marker/symbol line :: G</t>
+          <t>L100: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
         </is>
       </c>
       <c r="O11" s="1" t="inlineStr">
@@ -1263,12 +1275,12 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>38</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>35</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr"/>
@@ -1282,25 +1294,21 @@
       </c>
       <c r="I12" s="1" t="inlineStr">
         <is>
-          <t>L648: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | suspicious token(s): VanWarts (odd internal casing) :: VanWartsâ€™</t>
+          <t>L648: suspicious token(s): VanWarts (odd internal casing) :: VanWarts’</t>
         </is>
       </c>
       <c r="J12" s="1" t="inlineStr"/>
-      <c r="K12" s="1" t="inlineStr">
-        <is>
-          <t>L349: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: 'Fredericton, and if we donâ€™t tear it</t>
-        </is>
-      </c>
+      <c r="K12" s="1" t="inlineStr"/>
       <c r="L12" s="1" t="inlineStr"/>
       <c r="M12" s="1" t="inlineStr"/>
       <c r="N12" s="1" t="inlineStr">
         <is>
-          <t>L155: isolated marker/symbol line :: 1</t>
+          <t>L152: isolated marker/symbol line :: 8</t>
         </is>
       </c>
       <c r="O12" s="1" t="inlineStr">
         <is>
-          <t>L101: isolated marker/symbol line :: -</t>
+          <t>L66: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | symbol-only separator/garbage line | line starts with punctuation glued to text :: _________•</t>
         </is>
       </c>
       <c r="P12" s="1" t="inlineStr"/>
@@ -1327,7 +1335,7 @@
       </c>
       <c r="C13" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D13" s="1" t="inlineStr"/>
@@ -1345,21 +1353,17 @@
         </is>
       </c>
       <c r="J13" s="1" t="inlineStr"/>
-      <c r="K13" s="1" t="inlineStr">
-        <is>
-          <t>L467: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: air is fresh and pureâ€”a tonic to</t>
-        </is>
-      </c>
+      <c r="K13" s="1" t="inlineStr"/>
       <c r="L13" s="1" t="inlineStr"/>
       <c r="M13" s="1" t="inlineStr"/>
       <c r="N13" s="1" t="inlineStr">
         <is>
-          <t>L157: isolated marker/symbol line :: j</t>
+          <t>L154: isolated marker/symbol line :: G</t>
         </is>
       </c>
       <c r="O13" s="1" t="inlineStr">
         <is>
-          <t>L131: isolated marker/symbol line :: !</t>
+          <t>L101: isolated marker/symbol line :: -</t>
         </is>
       </c>
       <c r="P13" s="1" t="inlineStr"/>
@@ -1386,7 +1390,7 @@
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D14" s="1" t="inlineStr"/>
@@ -1400,21 +1404,17 @@
       </c>
       <c r="I14" s="1" t="inlineStr"/>
       <c r="J14" s="1" t="inlineStr"/>
-      <c r="K14" s="1" t="inlineStr">
-        <is>
-          <t>L490: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: from $2.50 upwardâ€” depending</t>
-        </is>
-      </c>
+      <c r="K14" s="1" t="inlineStr"/>
       <c r="L14" s="1" t="inlineStr"/>
       <c r="M14" s="1" t="inlineStr"/>
       <c r="N14" s="1" t="inlineStr">
         <is>
-          <t>L158: isolated marker/symbol line :: .</t>
+          <t>L155: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O14" s="1" t="inlineStr">
         <is>
-          <t>L252: isolated marker/symbol line :: /</t>
+          <t>L131: isolated marker/symbol line :: !</t>
         </is>
       </c>
       <c r="P14" s="1" t="inlineStr"/>
@@ -1455,21 +1455,17 @@
       </c>
       <c r="I15" s="1" t="inlineStr"/>
       <c r="J15" s="1" t="inlineStr"/>
-      <c r="K15" s="1" t="inlineStr">
-        <is>
-          <t>L595: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€”ATâ€”</t>
-        </is>
-      </c>
+      <c r="K15" s="1" t="inlineStr"/>
       <c r="L15" s="1" t="inlineStr"/>
       <c r="M15" s="1" t="inlineStr"/>
       <c r="N15" s="1" t="inlineStr">
         <is>
-          <t>L191: isolated marker/symbol line :: &amp;</t>
+          <t>L157: isolated marker/symbol line :: j</t>
         </is>
       </c>
       <c r="O15" s="1" t="inlineStr">
         <is>
-          <t>L260: isolated marker/symbol line :: K</t>
+          <t>L252: isolated marker/symbol line :: /</t>
         </is>
       </c>
       <c r="P15" s="1" t="inlineStr"/>
@@ -1510,21 +1506,17 @@
       </c>
       <c r="I16" s="1" t="inlineStr"/>
       <c r="J16" s="1" t="inlineStr"/>
-      <c r="K16" s="1" t="inlineStr">
-        <is>
-          <t>L648: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | suspicious token(s): VanWarts (odd internal casing) :: VanWartsâ€™</t>
-        </is>
-      </c>
+      <c r="K16" s="1" t="inlineStr"/>
       <c r="L16" s="1" t="inlineStr"/>
       <c r="M16" s="1" t="inlineStr"/>
       <c r="N16" s="1" t="inlineStr">
         <is>
-          <t>L192: isolated marker/symbol line :: &amp;</t>
+          <t>L158: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O16" s="1" t="inlineStr">
         <is>
-          <t>L282: isolated marker/symbol line :: 5</t>
+          <t>L260: isolated marker/symbol line :: K</t>
         </is>
       </c>
       <c r="P16" s="1" t="inlineStr"/>
@@ -1561,21 +1553,17 @@
       <c r="H17" s="1" t="inlineStr"/>
       <c r="I17" s="1" t="inlineStr"/>
       <c r="J17" s="1" t="inlineStr"/>
-      <c r="K17" s="1" t="inlineStr">
-        <is>
-          <t>L654: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: At last eveningâ€™s meeting of the</t>
-        </is>
-      </c>
+      <c r="K17" s="1" t="inlineStr"/>
       <c r="L17" s="1" t="inlineStr"/>
       <c r="M17" s="1" t="inlineStr"/>
       <c r="N17" s="1" t="inlineStr">
         <is>
-          <t>L194: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: â€�</t>
+          <t>L191: isolated marker/symbol line :: &amp;</t>
         </is>
       </c>
       <c r="O17" s="1" t="inlineStr">
         <is>
-          <t>L326: isolated marker/symbol line :: I</t>
+          <t>L282: isolated marker/symbol line :: 5</t>
         </is>
       </c>
       <c r="P17" s="1" t="inlineStr"/>
@@ -1600,21 +1588,17 @@
       <c r="H18" s="1" t="inlineStr"/>
       <c r="I18" s="1" t="inlineStr"/>
       <c r="J18" s="1" t="inlineStr"/>
-      <c r="K18" s="1" t="inlineStr">
-        <is>
-          <t>L713: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: When You Think Shoesâ€”Think Campbollâ€™s</t>
-        </is>
-      </c>
+      <c r="K18" s="1" t="inlineStr"/>
       <c r="L18" s="1" t="inlineStr"/>
       <c r="M18" s="1" t="inlineStr"/>
       <c r="N18" s="1" t="inlineStr">
         <is>
-          <t>L195: isolated marker/symbol line :: *</t>
+          <t>L192: isolated marker/symbol line :: &amp;</t>
         </is>
       </c>
       <c r="O18" s="1" t="inlineStr">
         <is>
-          <t>L327: isolated marker/symbol line :: +</t>
+          <t>L326: isolated marker/symbol line :: I</t>
         </is>
       </c>
       <c r="P18" s="1" t="inlineStr"/>
@@ -1639,21 +1623,17 @@
       <c r="H19" s="1" t="inlineStr"/>
       <c r="I19" s="1" t="inlineStr"/>
       <c r="J19" s="1" t="inlineStr"/>
-      <c r="K19" s="1" t="inlineStr">
-        <is>
-          <t>L765: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+02DC SMALL TILDE :: Gagetown ser â€˜ce.</t>
-        </is>
-      </c>
+      <c r="K19" s="1" t="inlineStr"/>
       <c r="L19" s="1" t="inlineStr"/>
       <c r="M19" s="1" t="inlineStr"/>
       <c r="N19" s="1" t="inlineStr">
         <is>
-          <t>L196: isolated marker/symbol line :: Y</t>
+          <t>L193: stray/suspicious non-ASCII glyph(s): U+4EAB CJK UNIFIED IDEOGRAPH-4EAB | isolated marker/symbol line :: 享</t>
         </is>
       </c>
       <c r="O19" s="1" t="inlineStr">
         <is>
-          <t>L392: isolated marker/symbol line :: #</t>
+          <t>L327: isolated marker/symbol line :: +</t>
         </is>
       </c>
       <c r="P19" s="1" t="inlineStr"/>
@@ -1683,12 +1663,12 @@
       <c r="M20" s="1" t="inlineStr"/>
       <c r="N20" s="1" t="inlineStr">
         <is>
-          <t>L197: isolated marker/symbol line :: 5</t>
+          <t>L194: isolated marker/symbol line :: ”</t>
         </is>
       </c>
       <c r="O20" s="1" t="inlineStr">
         <is>
-          <t>L402: isolated marker/symbol line :: :</t>
+          <t>L392: isolated marker/symbol line :: #</t>
         </is>
       </c>
       <c r="P20" s="1" t="inlineStr"/>
@@ -1718,12 +1698,12 @@
       <c r="M21" s="1" t="inlineStr"/>
       <c r="N21" s="1" t="inlineStr">
         <is>
-          <t>L216: isolated marker/symbol line :: &amp;</t>
+          <t>L195: isolated marker/symbol line :: *</t>
         </is>
       </c>
       <c r="O21" s="1" t="inlineStr">
         <is>
-          <t>L403: isolated marker/symbol line :: 1</t>
+          <t>L402: isolated marker/symbol line :: :</t>
         </is>
       </c>
       <c r="P21" s="1" t="inlineStr"/>
@@ -1753,12 +1733,12 @@
       <c r="M22" s="1" t="inlineStr"/>
       <c r="N22" s="1" t="inlineStr">
         <is>
-          <t>L226: isolated marker/symbol line :: L</t>
+          <t>L196: isolated marker/symbol line :: Y</t>
         </is>
       </c>
       <c r="O22" s="1" t="inlineStr">
         <is>
-          <t>L415: isolated marker/symbol line :: o</t>
+          <t>L403: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="P22" s="1" t="inlineStr"/>
@@ -1788,12 +1768,12 @@
       <c r="M23" s="1" t="inlineStr"/>
       <c r="N23" s="1" t="inlineStr">
         <is>
-          <t>L354: isolated marker/symbol line :: -</t>
+          <t>L197: isolated marker/symbol line :: 5</t>
         </is>
       </c>
       <c r="O23" s="1" t="inlineStr">
         <is>
-          <t>L452: isolated marker/symbol line :: I</t>
+          <t>L415: isolated marker/symbol line :: o</t>
         </is>
       </c>
       <c r="P23" s="1" t="inlineStr"/>
@@ -1823,12 +1803,12 @@
       <c r="M24" s="1" t="inlineStr"/>
       <c r="N24" s="1" t="inlineStr">
         <is>
-          <t>L397: isolated marker/symbol line :: Q</t>
+          <t>L216: isolated marker/symbol line :: &amp;</t>
         </is>
       </c>
       <c r="O24" s="1" t="inlineStr">
         <is>
-          <t>L453: isolated marker/symbol line :: F</t>
+          <t>L452: isolated marker/symbol line :: I</t>
         </is>
       </c>
       <c r="P24" s="1" t="inlineStr"/>
@@ -1858,12 +1838,12 @@
       <c r="M25" s="1" t="inlineStr"/>
       <c r="N25" s="1" t="inlineStr">
         <is>
-          <t>L398: isolated marker/symbol line :: G</t>
+          <t>L226: isolated marker/symbol line :: L</t>
         </is>
       </c>
       <c r="O25" s="1" t="inlineStr">
         <is>
-          <t>L497: isolated marker/symbol line :: 05</t>
+          <t>L453: isolated marker/symbol line :: F</t>
         </is>
       </c>
       <c r="P25" s="1" t="inlineStr"/>
@@ -1893,12 +1873,12 @@
       <c r="M26" s="1" t="inlineStr"/>
       <c r="N26" s="1" t="inlineStr">
         <is>
-          <t>L437: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | isolated marker/symbol line :: Â©</t>
+          <t>L354: isolated marker/symbol line :: -</t>
         </is>
       </c>
       <c r="O26" s="1" t="inlineStr">
         <is>
-          <t>L498: isolated marker/symbol line :: e</t>
+          <t>L497: isolated marker/symbol line :: 05</t>
         </is>
       </c>
       <c r="P26" s="1" t="inlineStr"/>
@@ -1928,12 +1908,12 @@
       <c r="M27" s="1" t="inlineStr"/>
       <c r="N27" s="1" t="inlineStr">
         <is>
-          <t>L466: isolated marker/symbol line :: 0</t>
+          <t>L397: isolated marker/symbol line :: Q</t>
         </is>
       </c>
       <c r="O27" s="1" t="inlineStr">
         <is>
-          <t>L543: isolated marker/symbol line :: ?</t>
+          <t>L498: isolated marker/symbol line :: e</t>
         </is>
       </c>
       <c r="P27" s="1" t="inlineStr"/>
@@ -1963,12 +1943,12 @@
       <c r="M28" s="1" t="inlineStr"/>
       <c r="N28" s="1" t="inlineStr">
         <is>
-          <t>L467: isolated marker/symbol line :: A</t>
+          <t>L398: isolated marker/symbol line :: G</t>
         </is>
       </c>
       <c r="O28" s="1" t="inlineStr">
         <is>
-          <t>L587: isolated marker/symbol line :: U</t>
+          <t>L543: isolated marker/symbol line :: ?</t>
         </is>
       </c>
       <c r="P28" s="1" t="inlineStr"/>
@@ -1998,12 +1978,12 @@
       <c r="M29" s="1" t="inlineStr"/>
       <c r="N29" s="1" t="inlineStr">
         <is>
-          <t>L468: isolated marker/symbol line :: 1</t>
+          <t>L437: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | isolated marker/symbol line :: ©</t>
         </is>
       </c>
       <c r="O29" s="1" t="inlineStr">
         <is>
-          <t>L604: isolated marker/symbol line :: U</t>
+          <t>L587: isolated marker/symbol line :: U</t>
         </is>
       </c>
       <c r="P29" s="1" t="inlineStr"/>
@@ -2033,12 +2013,12 @@
       <c r="M30" s="1" t="inlineStr"/>
       <c r="N30" s="1" t="inlineStr">
         <is>
-          <t>L500: isolated marker/symbol line :: &amp;</t>
+          <t>L466: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O30" s="1" t="inlineStr">
         <is>
-          <t>L606: isolated marker/symbol line :: I</t>
+          <t>L604: isolated marker/symbol line :: U</t>
         </is>
       </c>
       <c r="P30" s="1" t="inlineStr"/>
@@ -2068,12 +2048,12 @@
       <c r="M31" s="1" t="inlineStr"/>
       <c r="N31" s="1" t="inlineStr">
         <is>
-          <t>L507: isolated marker/symbol line :: C</t>
+          <t>L467: isolated marker/symbol line :: A</t>
         </is>
       </c>
       <c r="O31" s="1" t="inlineStr">
         <is>
-          <t>L608: isolated marker/symbol line :: w</t>
+          <t>L606: isolated marker/symbol line :: I</t>
         </is>
       </c>
       <c r="P31" s="1" t="inlineStr"/>
@@ -2103,12 +2083,12 @@
       <c r="M32" s="1" t="inlineStr"/>
       <c r="N32" s="1" t="inlineStr">
         <is>
-          <t>L653: symbol-only separator/garbage line :: $2.40</t>
+          <t>L468: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O32" s="1" t="inlineStr">
         <is>
-          <t>L610: isolated marker/symbol line :: I</t>
+          <t>L608: isolated marker/symbol line :: w</t>
         </is>
       </c>
       <c r="P32" s="1" t="inlineStr"/>
@@ -2138,12 +2118,12 @@
       <c r="M33" s="1" t="inlineStr"/>
       <c r="N33" s="1" t="inlineStr">
         <is>
-          <t>L665: isolated marker/symbol line :: T</t>
+          <t>L500: isolated marker/symbol line :: &amp;</t>
         </is>
       </c>
       <c r="O33" s="1" t="inlineStr">
         <is>
-          <t>L650: symbol-only separator/garbage line :: 77-</t>
+          <t>L610: isolated marker/symbol line :: I</t>
         </is>
       </c>
       <c r="P33" s="1" t="inlineStr"/>
@@ -2173,12 +2153,12 @@
       <c r="M34" s="1" t="inlineStr"/>
       <c r="N34" s="1" t="inlineStr">
         <is>
-          <t>L671: isolated marker/symbol line :: 8</t>
+          <t>L507: isolated marker/symbol line :: C</t>
         </is>
       </c>
       <c r="O34" s="1" t="inlineStr">
         <is>
-          <t>L774: symbol-only separator/garbage line :: $2.40</t>
+          <t>L650: symbol-only separator/garbage line :: 77-</t>
         </is>
       </c>
       <c r="P34" s="1" t="inlineStr"/>
@@ -2208,12 +2188,12 @@
       <c r="M35" s="1" t="inlineStr"/>
       <c r="N35" s="1" t="inlineStr">
         <is>
-          <t>L683: isolated marker/symbol line :: .</t>
+          <t>L653: symbol-only separator/garbage line :: $2.40</t>
         </is>
       </c>
       <c r="O35" s="1" t="inlineStr">
         <is>
-          <t>L805: isolated marker/symbol line :: 00</t>
+          <t>L774: symbol-only separator/garbage line :: $2.40</t>
         </is>
       </c>
       <c r="P35" s="1" t="inlineStr"/>
@@ -2227,6 +2207,134 @@
       <c r="X35" s="1" t="inlineStr"/>
       <c r="Y35" s="1" t="inlineStr"/>
     </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr"/>
+      <c r="B36" s="1" t="inlineStr"/>
+      <c r="C36" s="1" t="inlineStr"/>
+      <c r="D36" s="1" t="inlineStr"/>
+      <c r="E36" s="1" t="inlineStr"/>
+      <c r="F36" s="1" t="inlineStr"/>
+      <c r="G36" s="1" t="inlineStr"/>
+      <c r="H36" s="1" t="inlineStr"/>
+      <c r="I36" s="1" t="inlineStr"/>
+      <c r="J36" s="1" t="inlineStr"/>
+      <c r="K36" s="1" t="inlineStr"/>
+      <c r="L36" s="1" t="inlineStr"/>
+      <c r="M36" s="1" t="inlineStr"/>
+      <c r="N36" s="1" t="inlineStr">
+        <is>
+          <t>L665: isolated marker/symbol line :: T</t>
+        </is>
+      </c>
+      <c r="O36" s="1" t="inlineStr">
+        <is>
+          <t>L805: isolated marker/symbol line :: 00</t>
+        </is>
+      </c>
+      <c r="P36" s="1" t="inlineStr"/>
+      <c r="Q36" s="1" t="inlineStr"/>
+      <c r="R36" s="1" t="inlineStr"/>
+      <c r="S36" s="1" t="inlineStr"/>
+      <c r="T36" s="1" t="inlineStr"/>
+      <c r="U36" s="1" t="inlineStr"/>
+      <c r="V36" s="1" t="inlineStr"/>
+      <c r="W36" s="1" t="inlineStr"/>
+      <c r="X36" s="1" t="inlineStr"/>
+      <c r="Y36" s="1" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr"/>
+      <c r="B37" s="1" t="inlineStr"/>
+      <c r="C37" s="1" t="inlineStr"/>
+      <c r="D37" s="1" t="inlineStr"/>
+      <c r="E37" s="1" t="inlineStr"/>
+      <c r="F37" s="1" t="inlineStr"/>
+      <c r="G37" s="1" t="inlineStr"/>
+      <c r="H37" s="1" t="inlineStr"/>
+      <c r="I37" s="1" t="inlineStr"/>
+      <c r="J37" s="1" t="inlineStr"/>
+      <c r="K37" s="1" t="inlineStr"/>
+      <c r="L37" s="1" t="inlineStr"/>
+      <c r="M37" s="1" t="inlineStr"/>
+      <c r="N37" s="1" t="inlineStr">
+        <is>
+          <t>L671: isolated marker/symbol line :: 8</t>
+        </is>
+      </c>
+      <c r="O37" s="1" t="inlineStr"/>
+      <c r="P37" s="1" t="inlineStr"/>
+      <c r="Q37" s="1" t="inlineStr"/>
+      <c r="R37" s="1" t="inlineStr"/>
+      <c r="S37" s="1" t="inlineStr"/>
+      <c r="T37" s="1" t="inlineStr"/>
+      <c r="U37" s="1" t="inlineStr"/>
+      <c r="V37" s="1" t="inlineStr"/>
+      <c r="W37" s="1" t="inlineStr"/>
+      <c r="X37" s="1" t="inlineStr"/>
+      <c r="Y37" s="1" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr"/>
+      <c r="B38" s="1" t="inlineStr"/>
+      <c r="C38" s="1" t="inlineStr"/>
+      <c r="D38" s="1" t="inlineStr"/>
+      <c r="E38" s="1" t="inlineStr"/>
+      <c r="F38" s="1" t="inlineStr"/>
+      <c r="G38" s="1" t="inlineStr"/>
+      <c r="H38" s="1" t="inlineStr"/>
+      <c r="I38" s="1" t="inlineStr"/>
+      <c r="J38" s="1" t="inlineStr"/>
+      <c r="K38" s="1" t="inlineStr"/>
+      <c r="L38" s="1" t="inlineStr"/>
+      <c r="M38" s="1" t="inlineStr"/>
+      <c r="N38" s="1" t="inlineStr">
+        <is>
+          <t>L677: stray/suspicious non-ASCII glyph(s): U+56FD CJK UNIFIED IDEOGRAPH-56FD | isolated marker/symbol line :: 国</t>
+        </is>
+      </c>
+      <c r="O38" s="1" t="inlineStr"/>
+      <c r="P38" s="1" t="inlineStr"/>
+      <c r="Q38" s="1" t="inlineStr"/>
+      <c r="R38" s="1" t="inlineStr"/>
+      <c r="S38" s="1" t="inlineStr"/>
+      <c r="T38" s="1" t="inlineStr"/>
+      <c r="U38" s="1" t="inlineStr"/>
+      <c r="V38" s="1" t="inlineStr"/>
+      <c r="W38" s="1" t="inlineStr"/>
+      <c r="X38" s="1" t="inlineStr"/>
+      <c r="Y38" s="1" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr"/>
+      <c r="B39" s="1" t="inlineStr"/>
+      <c r="C39" s="1" t="inlineStr"/>
+      <c r="D39" s="1" t="inlineStr"/>
+      <c r="E39" s="1" t="inlineStr"/>
+      <c r="F39" s="1" t="inlineStr"/>
+      <c r="G39" s="1" t="inlineStr"/>
+      <c r="H39" s="1" t="inlineStr"/>
+      <c r="I39" s="1" t="inlineStr"/>
+      <c r="J39" s="1" t="inlineStr"/>
+      <c r="K39" s="1" t="inlineStr"/>
+      <c r="L39" s="1" t="inlineStr"/>
+      <c r="M39" s="1" t="inlineStr"/>
+      <c r="N39" s="1" t="inlineStr">
+        <is>
+          <t>L683: isolated marker/symbol line :: .</t>
+        </is>
+      </c>
+      <c r="O39" s="1" t="inlineStr"/>
+      <c r="P39" s="1" t="inlineStr"/>
+      <c r="Q39" s="1" t="inlineStr"/>
+      <c r="R39" s="1" t="inlineStr"/>
+      <c r="S39" s="1" t="inlineStr"/>
+      <c r="T39" s="1" t="inlineStr"/>
+      <c r="U39" s="1" t="inlineStr"/>
+      <c r="V39" s="1" t="inlineStr"/>
+      <c r="W39" s="1" t="inlineStr"/>
+      <c r="X39" s="1" t="inlineStr"/>
+      <c r="Y39" s="1" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
